--- a/data/trans_orig/Q25_A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q25_A_R-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en años desde que dejó de fumar</t>
+          <t>Tiempo medio en años desde que dejó de fumar (tasa de respuesta: 96,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,65; 13,33</t>
+          <t>8,95; 13,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,36; 15,16</t>
+          <t>11,02; 14,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,71; 16,52</t>
+          <t>11,83; 16,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,06; 18,64</t>
+          <t>14,06; 18,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,13; 10,76</t>
+          <t>6,06; 10,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 8,62</t>
+          <t>5,02; 9,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,8; 13,79</t>
+          <t>8,68; 13,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,86; 16,52</t>
+          <t>12,06; 16,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,33; 11,92</t>
+          <t>8,45; 11,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,4; 12,4</t>
+          <t>9,48; 12,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,15; 14,56</t>
+          <t>10,98; 14,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,1; 17,46</t>
+          <t>13,89; 17,21</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,92; 12,02</t>
+          <t>8,01; 12,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,31; 15,36</t>
+          <t>9,33; 15,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,64; 13,84</t>
+          <t>9,66; 13,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,31; 18,15</t>
+          <t>13,75; 18,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,67; 9,35</t>
+          <t>4,56; 9,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,53; 10,9</t>
+          <t>6,54; 10,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,43; 10,28</t>
+          <t>6,57; 9,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,94; 14,72</t>
+          <t>10,08; 15,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,26; 10,38</t>
+          <t>7,37; 10,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,93; 12,97</t>
+          <t>8,82; 13,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,48; 11,56</t>
+          <t>8,68; 11,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,81; 16,22</t>
+          <t>12,81; 16,34</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,82; 11,55</t>
+          <t>8,75; 11,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,26; 13,79</t>
+          <t>10,38; 14,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,78; 15,99</t>
+          <t>11,71; 16,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 16,78</t>
+          <t>2,87; 16,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,3</t>
+          <t>3,59; 7,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,57; 11,01</t>
+          <t>5,85; 11,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,66; 11,7</t>
+          <t>4,7; 11,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,01; 13,5</t>
+          <t>7,91; 13,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,06; 10,63</t>
+          <t>7,9; 10,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,79; 13,04</t>
+          <t>9,79; 12,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,23; 14,95</t>
+          <t>11,19; 15,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 15,68</t>
+          <t>3,0; 15,66</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,27; 12,52</t>
+          <t>10,3; 12,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,26; 12,88</t>
+          <t>10,36; 13,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,02; 12,47</t>
+          <t>9,93; 12,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,5; 18,78</t>
+          <t>15,45; 18,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,77; 8,33</t>
+          <t>4,76; 8,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,44; 9,39</t>
+          <t>6,3; 9,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,97; 10,44</t>
+          <t>7,07; 10,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,31; 12,91</t>
+          <t>9,18; 12,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,29; 11,16</t>
+          <t>9,32; 11,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,49; 11,56</t>
+          <t>9,4; 11,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,5; 11,46</t>
+          <t>9,45; 11,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,04; 16,86</t>
+          <t>13,94; 16,63</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,95; 15,1</t>
+          <t>10,21; 15,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,66; 15,96</t>
+          <t>11,38; 15,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,82; 16,82</t>
+          <t>12,8; 16,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,2; 18,68</t>
+          <t>14,44; 18,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,45; 8,17</t>
+          <t>4,58; 8,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 9,44</t>
+          <t>6,34; 9,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,58; 13,89</t>
+          <t>7,62; 13,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,3; 14,82</t>
+          <t>10,4; 14,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,46; 12,2</t>
+          <t>8,39; 12,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,98; 13,07</t>
+          <t>9,88; 12,88</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,25; 14,68</t>
+          <t>11,15; 14,56</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,07; 16,18</t>
+          <t>12,93; 16,21</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,04</t>
+          <t>0,86; 6,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,22; 16,77</t>
+          <t>1,17; 14,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,06; 16,37</t>
+          <t>1,0; 16,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,47; 15,45</t>
+          <t>2,72; 15,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,31; 10,33</t>
+          <t>6,49; 10,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,05; 10,78</t>
+          <t>5,79; 10,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,72; 9,64</t>
+          <t>4,99; 9,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,17; 23,81</t>
+          <t>13,44; 24,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,87; 9,84</t>
+          <t>5,78; 9,66</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,95; 10,13</t>
+          <t>5,96; 10,07</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,69; 9,45</t>
+          <t>4,79; 9,62</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,48; 22,02</t>
+          <t>12,37; 23,05</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,11; 11,58</t>
+          <t>10,04; 11,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1566,52 +1566,52 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,84; 13,43</t>
+          <t>11,78; 13,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,74; 16,62</t>
+          <t>6,41; 16,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,94; 7,71</t>
+          <t>5,96; 7,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,9; 8,43</t>
+          <t>6,94; 8,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,85; 9,83</t>
+          <t>7,96; 9,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,79; 14,07</t>
+          <t>11,74; 14,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,02; 10,25</t>
+          <t>9,1; 10,25</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,05; 11,36</t>
+          <t>10,04; 11,25</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,72; 12,02</t>
+          <t>10,7; 11,94</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,99; 15,36</t>
+          <t>6,87; 15,32</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q25_A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q25_A_R-Clase-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,46</t>
+          <t>16,73</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>14,15</t>
+          <t>14,82</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,66</t>
+          <t>16,07</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,95; 13,6</t>
+          <t>8,56; 13,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,02; 14,84</t>
+          <t>11,17; 14,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,83; 16,79</t>
+          <t>11,89; 16,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,06; 18,33</t>
+          <t>14,59; 18,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,06; 10,38</t>
+          <t>6,23; 10,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 9,09</t>
+          <t>4,85; 8,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,68; 13,43</t>
+          <t>8,64; 13,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,06; 16,64</t>
+          <t>12,83; 17,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,45; 11,96</t>
+          <t>8,39; 11,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,48; 12,54</t>
+          <t>9,37; 12,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,98; 14,62</t>
+          <t>11,12; 14,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,89; 17,21</t>
+          <t>14,34; 17,65</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,71</t>
+          <t>15,54</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,3</t>
+          <t>12,81</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,43</t>
+          <t>14,5</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,01; 12,01</t>
+          <t>7,98; 12,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,33; 15,69</t>
+          <t>9,44; 15,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,66; 13,9</t>
+          <t>9,62; 13,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,75; 18,36</t>
+          <t>13,34; 18,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 9,28</t>
+          <t>4,46; 8,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,54; 10,89</t>
+          <t>6,55; 10,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,57; 9,96</t>
+          <t>6,43; 10,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,08; 15,03</t>
+          <t>10,47; 15,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,37; 10,44</t>
+          <t>7,26; 10,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,82; 13,31</t>
+          <t>8,76; 13,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,68; 11,44</t>
+          <t>8,69; 11,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,81; 16,34</t>
+          <t>12,96; 16,36</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,98</t>
+          <t>16,14</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,75</t>
+          <t>10,67</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,26</t>
+          <t>15,17</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,75; 11,66</t>
+          <t>8,76; 11,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,38; 14,1</t>
+          <t>10,28; 13,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,71; 16,05</t>
+          <t>11,83; 15,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 16,65</t>
+          <t>14,33; 18,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 7,04</t>
+          <t>3,55; 7,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,85; 11,13</t>
+          <t>5,78; 10,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,7; 11,2</t>
+          <t>4,48; 11,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,91; 13,87</t>
+          <t>7,81; 13,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,9; 10,53</t>
+          <t>8,07; 10,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,79; 12,96</t>
+          <t>10,02; 13,12</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,19; 15,27</t>
+          <t>11,27; 15,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,0; 15,66</t>
+          <t>13,52; 17,09</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,08</t>
+          <t>16,82</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,95</t>
+          <t>11,0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,28</t>
+          <t>15,16</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,3; 12,36</t>
+          <t>10,3; 12,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,36; 13,01</t>
+          <t>10,31; 12,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,93; 12,44</t>
+          <t>9,97; 12,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,45; 18,75</t>
+          <t>15,25; 18,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,76; 8,55</t>
+          <t>4,68; 8,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 9,32</t>
+          <t>6,49; 9,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,07; 10,57</t>
+          <t>6,98; 10,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,18; 12,95</t>
+          <t>9,37; 13,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,32; 11,22</t>
+          <t>9,32; 11,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,4; 11,6</t>
+          <t>9,53; 11,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,45; 11,42</t>
+          <t>9,4; 11,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,94; 16,63</t>
+          <t>13,9; 16,42</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,44</t>
+          <t>16,23</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,39</t>
+          <t>11,84</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,62</t>
+          <t>14,2</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1276,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,21; 15,59</t>
+          <t>10,14; 15,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,38; 15,73</t>
+          <t>11,46; 16,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,8; 16,74</t>
+          <t>12,73; 16,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,44; 18,53</t>
+          <t>14,08; 18,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,58; 8,29</t>
+          <t>4,61; 8,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,34; 9,48</t>
+          <t>6,29; 9,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,62; 13,47</t>
+          <t>7,53; 13,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,4; 14,83</t>
+          <t>9,78; 13,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,39; 12,39</t>
+          <t>8,28; 12,32</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,88; 12,88</t>
+          <t>9,98; 13,08</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,15; 14,56</t>
+          <t>11,3; 14,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,93; 16,21</t>
+          <t>12,72; 15,67</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7,75</t>
+          <t>8,19</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17,56</t>
+          <t>15,37</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,99</t>
+          <t>14,28</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,86; 6,9</t>
+          <t>0,89; 7,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,17; 14,21</t>
+          <t>1,29; 15,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 16,68</t>
+          <t>0,97; 15,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,72; 15,53</t>
+          <t>2,75; 15,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,49; 10,62</t>
+          <t>6,28; 10,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,79; 10,36</t>
+          <t>5,8; 10,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,99; 9,65</t>
+          <t>4,94; 10,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,44; 24,52</t>
+          <t>12,04; 19,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,66</t>
+          <t>5,83; 9,96</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,96; 10,07</t>
+          <t>5,84; 10,22</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,62</t>
+          <t>4,95; 9,44</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,37; 23,05</t>
+          <t>11,25; 17,88</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12,17</t>
+          <t>16,32</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>12,85</t>
+          <t>12,7</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,36</t>
+          <t>15,03</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,04; 11,57</t>
+          <t>10,14; 11,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,28; 12,97</t>
+          <t>11,25; 12,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,78; 13,46</t>
+          <t>11,88; 13,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,41; 16,55</t>
+          <t>15,38; 17,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,96; 7,65</t>
+          <t>5,98; 7,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,94; 8,46</t>
+          <t>6,98; 8,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,96; 9,97</t>
+          <t>7,95; 9,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,74; 14,07</t>
+          <t>11,71; 13,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,1; 10,25</t>
+          <t>9,1; 10,32</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,04; 11,25</t>
+          <t>10,06; 11,28</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,7; 11,94</t>
+          <t>10,69; 11,96</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,87; 15,32</t>
+          <t>14,38; 15,68</t>
         </is>
       </c>
     </row>
